--- a/exports/trend_1d/BANDHANBNK_full_report.xlsx
+++ b/exports/trend_1d/BANDHANBNK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>11.23</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H2" t="n">
-        <v>479.55</v>
+        <v>468.8</v>
       </c>
       <c r="I2" t="n">
         <v>475.6494</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.32</v>
+        <v>-12.33</v>
       </c>
       <c r="L2" t="n">
-        <v>11.45</v>
+        <v>13.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
         <v>2.68</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43259</v>
+        <v>43262</v>
       </c>
       <c r="H3" t="n">
-        <v>498.1</v>
+        <v>512.2</v>
       </c>
       <c r="I3" t="n">
         <v>503.3767717189936</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.25</v>
+        <v>-9.26</v>
       </c>
       <c r="L3" t="n">
-        <v>7.42</v>
+        <v>12.84</v>
       </c>
       <c r="M3" t="n">
         <v>1.37</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H4" t="n">
-        <v>646.3</v>
+        <v>620.25</v>
       </c>
       <c r="I4" t="n">
         <v>634.5300874488255</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="n">
-        <v>26.18</v>
+        <v>21.1</v>
       </c>
       <c r="L4" t="n">
         <v>3.15</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H5" t="n">
-        <v>459.75</v>
+        <v>476.2</v>
       </c>
       <c r="I5" t="n">
         <v>461.4879325595515</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" t="n">
-        <v>25.88</v>
+        <v>23.22</v>
       </c>
       <c r="L5" t="n">
         <v>5.97</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.46</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="H6" t="n">
-        <v>528.9</v>
+        <v>498.05</v>
       </c>
       <c r="I6" t="n">
         <v>500.5335809501651</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K6" t="n">
-        <v>11.07</v>
+        <v>4.59</v>
       </c>
       <c r="L6" t="n">
         <v>7.17</v>
@@ -783,7 +854,7 @@
         <v>2.12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.38</v>
+        <v>5.83</v>
       </c>
       <c r="O6" t="n">
         <v>3.58</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43502</v>
+        <v>43503</v>
       </c>
       <c r="H7" t="n">
-        <v>440.4</v>
+        <v>460.45</v>
       </c>
       <c r="I7" t="n">
         <v>450.9598542353276</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>11.58</v>
+        <v>7.55</v>
       </c>
       <c r="L7" t="n">
         <v>8.82</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.77</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H8" t="n">
-        <v>574.7</v>
+        <v>553.25</v>
       </c>
       <c r="I8" t="n">
         <v>562.5063611386877</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K8" t="n">
-        <v>24.81</v>
+        <v>20.15</v>
       </c>
       <c r="L8" t="n">
         <v>3.36</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>13.33</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43607</v>
+        <v>43608</v>
       </c>
       <c r="H9" t="n">
-        <v>599.55</v>
+        <v>615.95</v>
       </c>
       <c r="I9" t="n">
         <v>608.4828010670853</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.369999999999999</v>
+        <v>-11.33</v>
       </c>
       <c r="L9" t="n">
-        <v>12.07</v>
+        <v>13.86</v>
       </c>
       <c r="M9" t="n">
         <v>5.17</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>11.96</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H10" t="n">
-        <v>546.55</v>
+        <v>538.65</v>
       </c>
       <c r="I10" t="n">
         <v>542.2669352437964</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>-11.27</v>
+        <v>-12.55</v>
       </c>
       <c r="L10" t="n">
-        <v>12.64</v>
+        <v>13.58</v>
       </c>
       <c r="M10" t="n">
         <v>1.78</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H11" t="n">
-        <v>443.95</v>
+        <v>496.95</v>
       </c>
       <c r="I11" t="n">
         <v>481.6573045022178</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" t="n">
-        <v>17.58</v>
+        <v>7.74</v>
       </c>
       <c r="L11" t="n">
         <v>5.47</v>
@@ -1068,7 +1199,7 @@
         <v>5.25</v>
       </c>
       <c r="N11" t="n">
-        <v>6.24</v>
+        <v>11.94</v>
       </c>
       <c r="O11" t="n">
         <v>-1.45</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>14.08</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H12" t="n">
-        <v>543.2</v>
+        <v>521.05</v>
       </c>
       <c r="I12" t="n">
         <v>524.0594191837415</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K12" t="n">
-        <v>9.31</v>
+        <v>4.85</v>
       </c>
       <c r="L12" t="n">
         <v>10.56</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.16</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H13" t="n">
-        <v>247.7</v>
+        <v>263.25</v>
       </c>
       <c r="I13" t="n">
         <v>256.143681730972</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K13" t="n">
-        <v>52.46</v>
+        <v>49.48</v>
       </c>
       <c r="L13" t="n">
         <v>5.56</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>20.51</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H14" t="n">
-        <v>345.1</v>
+        <v>308.8</v>
       </c>
       <c r="I14" t="n">
         <v>316.5342861604375</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>31.09</v>
+        <v>17.3</v>
       </c>
       <c r="L14" t="n">
         <v>5.58</v>
       </c>
       <c r="M14" t="n">
-        <v>6.54</v>
+        <v>7.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.56</v>
+        <v>10.52</v>
       </c>
       <c r="O14" t="n">
         <v>6.28</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>18.66</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H15" t="n">
-        <v>292.35</v>
+        <v>306</v>
       </c>
       <c r="I15" t="n">
         <v>298.7798032739914</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" t="n">
-        <v>5.33</v>
+        <v>0.91</v>
       </c>
       <c r="L15" t="n">
         <v>6.33</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.83</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H16" t="n">
-        <v>408.2</v>
+        <v>374.3</v>
       </c>
       <c r="I16" t="n">
         <v>377.758969589543</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K16" t="n">
-        <v>33.4</v>
+        <v>22.32</v>
       </c>
       <c r="L16" t="n">
         <v>8.82</v>
@@ -1353,7 +1544,7 @@
         <v>1.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>4.67</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44277</v>
+        <v>44278</v>
       </c>
       <c r="H17" t="n">
-        <v>352.6</v>
+        <v>364.65</v>
       </c>
       <c r="I17" t="n">
         <v>358.4432978688282</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>2.58</v>
       </c>
       <c r="L17" t="n">
         <v>13.52</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44301</v>
+        <v>44302</v>
       </c>
       <c r="H18" t="n">
-        <v>326.2</v>
+        <v>322.65</v>
       </c>
       <c r="I18" t="n">
         <v>324.0836658987952</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.54</v>
+        <v>-11.52</v>
       </c>
       <c r="L18" t="n">
         <v>12.94</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.04</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44351</v>
+        <v>44354</v>
       </c>
       <c r="H19" t="n">
-        <v>314.85</v>
+        <v>320</v>
       </c>
       <c r="I19" t="n">
         <v>318.6555912536159</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K19" t="n">
-        <v>2.42</v>
+        <v>0.82</v>
       </c>
       <c r="L19" t="n">
         <v>5.36</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>9.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44392</v>
+        <v>44393</v>
       </c>
       <c r="H20" t="n">
-        <v>319.7</v>
+        <v>309.15</v>
       </c>
       <c r="I20" t="n">
         <v>312.6165489117453</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.09</v>
+        <v>-3.39</v>
       </c>
       <c r="L20" t="n">
         <v>4.25</v>
       </c>
       <c r="M20" t="n">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.64</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H21" t="n">
-        <v>291.15</v>
+        <v>297.65</v>
       </c>
       <c r="I21" t="n">
         <v>291.4211663801874</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K21" t="n">
-        <v>5.82</v>
+        <v>3.72</v>
       </c>
       <c r="L21" t="n">
         <v>2.38</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.76</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44495</v>
+        <v>44496</v>
       </c>
       <c r="H22" t="n">
-        <v>305.4</v>
+        <v>296.15</v>
       </c>
       <c r="I22" t="n">
         <v>304.9466531453165</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L22" t="n">
         <v>7.79</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.78</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H23" t="n">
-        <v>277.35</v>
+        <v>283.65</v>
       </c>
       <c r="I23" t="n">
         <v>277.8651734197933</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>6.35</v>
+        <v>4.22</v>
       </c>
       <c r="L23" t="n">
         <v>7.68</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H24" t="n">
-        <v>315.45</v>
+        <v>291.15</v>
       </c>
       <c r="I24" t="n">
         <v>292.4601976010036</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>11.21</v>
+        <v>2.64</v>
       </c>
       <c r="L24" t="n">
         <v>1.99</v>
       </c>
       <c r="M24" t="n">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>7.7</v>
       </c>
       <c r="O24" t="n">
         <v>2.27</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.79</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H25" t="n">
-        <v>294.45</v>
+        <v>301.5</v>
       </c>
       <c r="I25" t="n">
         <v>299.4861383904075</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.13</v>
+        <v>-3.55</v>
       </c>
       <c r="L25" t="n">
         <v>7.45</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>14.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H26" t="n">
-        <v>310.4</v>
+        <v>274.05</v>
       </c>
       <c r="I26" t="n">
         <v>301.8626227323152</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>2.95</v>
+        <v>-9.1</v>
       </c>
       <c r="L26" t="n">
-        <v>7.05</v>
+        <v>12.47</v>
       </c>
       <c r="M26" t="n">
         <v>2.99</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>11.71</v>
       </c>
       <c r="O26" t="n">
         <v>2.39</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>22.6</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44797</v>
+        <v>44798</v>
       </c>
       <c r="H27" t="n">
-        <v>295.75</v>
+        <v>297.15</v>
       </c>
       <c r="I27" t="n">
         <v>296.6426312358701</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.92</v>
+        <v>-8.43</v>
       </c>
       <c r="L27" t="n">
         <v>14.54</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H28" t="n">
-        <v>287.25</v>
+        <v>278.15</v>
       </c>
       <c r="I28" t="n">
         <v>278.7125744616914</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.33</v>
+        <v>-6.39</v>
       </c>
       <c r="L28" t="n">
         <v>8.6</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.66</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44893</v>
+        <v>44894</v>
       </c>
       <c r="H29" t="n">
-        <v>224.35</v>
+        <v>234.15</v>
       </c>
       <c r="I29" t="n">
         <v>234.0035654424383</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K29" t="n">
-        <v>19.34</v>
+        <v>15.82</v>
       </c>
       <c r="L29" t="n">
         <v>3.24</v>
@@ -2094,7 +2441,7 @@
         <v>1.99</v>
       </c>
       <c r="N29" t="n">
-        <v>3.43</v>
+        <v>4.37</v>
       </c>
       <c r="O29" t="n">
         <v>-3.17</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>11.28</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H30" t="n">
-        <v>231.75</v>
+        <v>226.5</v>
       </c>
       <c r="I30" t="n">
         <v>231.5748368687193</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.02</v>
+        <v>-3.27</v>
       </c>
       <c r="L30" t="n">
         <v>4.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0.27</v>
+        <v>1.36</v>
       </c>
       <c r="N30" t="n">
         <v>4.69</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.82</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45034</v>
+        <v>45035</v>
       </c>
       <c r="H31" t="n">
-        <v>213.3</v>
+        <v>214.35</v>
       </c>
       <c r="I31" t="n">
         <v>213.5508781748507</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K31" t="n">
-        <v>5.83</v>
+        <v>5.36</v>
       </c>
       <c r="L31" t="n">
         <v>10.71</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.55</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45091</v>
+        <v>45092</v>
       </c>
       <c r="H32" t="n">
-        <v>252.55</v>
+        <v>246.95</v>
       </c>
       <c r="I32" t="n">
         <v>249.1612863734594</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K32" t="n">
-        <v>17.82</v>
+        <v>15.21</v>
       </c>
       <c r="L32" t="n">
         <v>2.17</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45160</v>
+        <v>45161</v>
       </c>
       <c r="H33" t="n">
-        <v>232.1</v>
+        <v>237.25</v>
       </c>
       <c r="I33" t="n">
         <v>233.6201622444409</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K33" t="n">
-        <v>6.01</v>
+        <v>3.93</v>
       </c>
       <c r="L33" t="n">
         <v>3.36</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>7.65</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H34" t="n">
-        <v>238.1</v>
+        <v>229.15</v>
       </c>
       <c r="I34" t="n">
         <v>232.9646575025962</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K34" t="n">
-        <v>0.36</v>
+        <v>-3.41</v>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>4.03</v>
       </c>
       <c r="M34" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="N34" t="n">
         <v>4.22</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.84</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H35" t="n">
-        <v>222.35</v>
+        <v>226.1</v>
       </c>
       <c r="I35" t="n">
         <v>224.5770154523427</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K35" t="n">
-        <v>2.97</v>
+        <v>1.33</v>
       </c>
       <c r="L35" t="n">
         <v>2.77</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.94</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H36" t="n">
-        <v>251.7</v>
+        <v>233.1</v>
       </c>
       <c r="I36" t="n">
         <v>234.3500305615101</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>11.32</v>
+        <v>3.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.37</v>
@@ -2493,7 +2924,7 @@
         <v>0.77</v>
       </c>
       <c r="N36" t="n">
-        <v>3.72</v>
+        <v>7.39</v>
       </c>
       <c r="O36" t="n">
         <v>1.69</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H37" t="n">
-        <v>190.5</v>
+        <v>197.95</v>
       </c>
       <c r="I37" t="n">
         <v>195.1958632724957</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K37" t="n">
-        <v>18.28</v>
+        <v>15.08</v>
       </c>
       <c r="L37" t="n">
         <v>8.109999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H38" t="n">
-        <v>184.95</v>
+        <v>182.7</v>
       </c>
       <c r="I38" t="n">
         <v>182.886879946224</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.57</v>
+        <v>-7.7</v>
       </c>
       <c r="L38" t="n">
         <v>9.449999999999999</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.13</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H39" t="n">
-        <v>188.3</v>
+        <v>190.75</v>
       </c>
       <c r="I39" t="n">
         <v>189.649493228444</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.07</v>
+        <v>-4.41</v>
       </c>
       <c r="L39" t="n">
-        <v>4.05</v>
+        <v>4.71</v>
       </c>
       <c r="M39" t="n">
         <v>1.27</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.73</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H40" t="n">
-        <v>195.52</v>
+        <v>188.1</v>
       </c>
       <c r="I40" t="n">
         <v>190.2279305389943</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>2.5</v>
+        <v>-1.39</v>
       </c>
       <c r="L40" t="n">
         <v>11.32</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>14.02</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="H41" t="n">
-        <v>192.5</v>
+        <v>218.87</v>
       </c>
       <c r="I41" t="n">
         <v>208.0676624642918</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.34</v>
+        <v>-16.36</v>
       </c>
       <c r="L41" t="n">
-        <v>5.48</v>
+        <v>16.96</v>
       </c>
       <c r="M41" t="n">
-        <v>0.25</v>
+        <v>5.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3.59</v>
+        <v>13.7</v>
       </c>
       <c r="O41" t="n">
         <v>-3.8</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>16.55</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H42" t="n">
-        <v>197.05</v>
+        <v>192.6</v>
       </c>
       <c r="I42" t="n">
         <v>193.0281340635313</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>-9.970000000000001</v>
+        <v>-12</v>
       </c>
       <c r="L42" t="n">
-        <v>10.27</v>
+        <v>12.59</v>
       </c>
       <c r="M42" t="n">
         <v>2.98</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="H43" t="n">
-        <v>207.68</v>
+        <v>213.13</v>
       </c>
       <c r="I43" t="n">
         <v>210.5348491258593</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.83</v>
+        <v>-10.66</v>
       </c>
       <c r="L43" t="n">
-        <v>9.59</v>
+        <v>11.21</v>
       </c>
       <c r="M43" t="n">
         <v>1.32</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H44" t="n">
-        <v>195.28</v>
+        <v>189.01</v>
       </c>
       <c r="I44" t="n">
         <v>193.4624744619677</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.380000000000001</v>
+        <v>-11.32</v>
       </c>
       <c r="L44" t="n">
-        <v>8.51</v>
+        <v>11.72</v>
       </c>
       <c r="M44" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="N44" t="n">
-        <v>2.33</v>
+        <v>3.21</v>
       </c>
       <c r="O44" t="n">
         <v>2.62</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.2</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H45" t="n">
-        <v>187.7</v>
+        <v>210.26</v>
       </c>
       <c r="I45" t="n">
         <v>204.133559779458</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6899999999999999</v>
+        <v>-11.24</v>
       </c>
       <c r="L45" t="n">
-        <v>2.77</v>
+        <v>12.06</v>
       </c>
       <c r="M45" t="n">
-        <v>1.68</v>
+        <v>7.62</v>
       </c>
       <c r="N45" t="n">
-        <v>1.8</v>
+        <v>12.02</v>
       </c>
       <c r="O45" t="n">
         <v>-3.21</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H46" t="n">
-        <v>184.89</v>
+        <v>173.8</v>
       </c>
       <c r="I46" t="n">
         <v>183.1350149207751</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.07</v>
+        <v>-17.34</v>
       </c>
       <c r="L46" t="n">
-        <v>12.49</v>
+        <v>17.72</v>
       </c>
       <c r="M46" t="n">
-        <v>0.17</v>
+        <v>1.29</v>
       </c>
       <c r="N46" t="n">
-        <v>4.85</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>12.02</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>15.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="H47" t="n">
-        <v>140.23</v>
+        <v>147.35</v>
       </c>
       <c r="I47" t="n">
         <v>145.9409898759063</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K47" t="n">
-        <v>19.32</v>
+        <v>15.22</v>
       </c>
       <c r="L47" t="n">
         <v>9.140000000000001</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>15.67</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="H48" t="n">
-        <v>175.03</v>
+        <v>173.44</v>
       </c>
       <c r="I48" t="n">
         <v>174.5655868489618</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K48" t="n">
-        <v>18.79</v>
+        <v>17.71</v>
       </c>
       <c r="L48" t="n">
         <v>6.61</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.81</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H49" t="n">
-        <v>174.28</v>
+        <v>176.82</v>
       </c>
       <c r="I49" t="n">
         <v>176.3744479417825</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.48</v>
+        <v>-1.95</v>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="M49" t="n">
         <v>0.99</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>8.23</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H50" t="n">
-        <v>162.93</v>
+        <v>161.8</v>
       </c>
       <c r="I50" t="n">
         <v>162.2698662053965</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.86</v>
+        <v>-8.49</v>
       </c>
       <c r="L50" t="n">
-        <v>8.1</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>0.53</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.16</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H51" t="n">
-        <v>163.3</v>
+        <v>169.32</v>
       </c>
       <c r="I51" t="n">
         <v>167.8125238138763</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.93</v>
+        <v>-4.65</v>
       </c>
       <c r="L51" t="n">
-        <v>4.38</v>
+        <v>5.12</v>
       </c>
       <c r="M51" t="n">
         <v>0.9399999999999999</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H52" t="n">
-        <v>170.58</v>
+        <v>156.56</v>
       </c>
       <c r="I52" t="n">
         <v>160.8391436082169</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>0.74</v>
+        <v>-7.54</v>
       </c>
       <c r="L52" t="n">
-        <v>5.85</v>
+        <v>7.86</v>
       </c>
       <c r="M52" t="n">
-        <v>0.78</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O52" t="n">
         <v>3.69</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.87</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="H53" t="n">
-        <v>149.57</v>
+        <v>151.79</v>
       </c>
       <c r="I53" t="n">
         <v>149.7783394185465</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K53" t="n">
-        <v>4.46</v>
+        <v>3.05</v>
       </c>
       <c r="L53" t="n">
         <v>5.33</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.48</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="H54" t="n">
-        <v>175.5</v>
+        <v>162.54</v>
       </c>
       <c r="I54" t="n">
         <v>170.6818692202617</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K54" t="n">
-        <v>15.62</v>
+        <v>7.08</v>
       </c>
       <c r="L54" t="n">
         <v>9.81</v>
@@ -3519,7 +4166,7 @@
         <v>2.77</v>
       </c>
       <c r="N54" t="n">
-        <v>4.87</v>
+        <v>7.38</v>
       </c>
       <c r="O54" t="n">
         <v>1.48</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>15.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H55" t="n">
-        <v>164.75</v>
+        <v>165.94</v>
       </c>
       <c r="I55" t="n">
         <v>165.3525853010086</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.36</v>
+        <v>-2.09</v>
       </c>
       <c r="L55" t="n">
         <v>8.51</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>14.83</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H56" t="n">
-        <v>208.83</v>
+        <v>173.5</v>
       </c>
       <c r="I56" t="n">
         <v>193.1286983565722</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K56" t="n">
-        <v>25.85</v>
+        <v>4.56</v>
       </c>
       <c r="L56" t="n">
         <v>2.76</v>
       </c>
       <c r="M56" t="n">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="N56" t="n">
-        <v>4.72</v>
+        <v>16.92</v>
       </c>
       <c r="O56" t="n">
         <v>0.72</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>22.44</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="H57" t="n">
-        <v>171.7</v>
+        <v>174</v>
       </c>
       <c r="I57" t="n">
         <v>173.693169655604</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
-        <v>1.04</v>
+        <v>-0.29</v>
       </c>
       <c r="L57" t="n">
         <v>10.79</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="H58" t="n">
-        <v>176</v>
+        <v>168.27</v>
       </c>
       <c r="I58" t="n">
         <v>172.0508546893819</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>1.15</v>
+        <v>-3.29</v>
       </c>
       <c r="L58" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="M58" t="n">
         <v>2.81</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>17</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7473,7 +8188,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="6">
@@ -7483,7 +8198,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -7493,7 +8208,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8">
@@ -7503,7 +8218,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7513,7 +8228,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -7523,7 +8238,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="11">
@@ -7533,7 +8248,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -7543,7 +8258,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -7553,7 +8268,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -7563,7 +8278,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.91</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="15">
@@ -7573,7 +8288,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="16">
@@ -7583,7 +8298,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.12</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17">
@@ -7593,7 +8308,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52.46</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="18">
@@ -7603,7 +8318,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="19">
@@ -7613,7 +8328,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.98</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="20">
@@ -7623,7 +8338,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.05</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="21">
@@ -7633,7 +8348,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.54</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="22">
@@ -7643,7 +8358,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -7653,7 +8368,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -7663,7 +8378,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="25">
@@ -7683,7 +8398,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.54</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="27">
@@ -7703,7 +8418,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
